--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/1.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/1.xlsx
@@ -426,13 +426,13 @@
         <v>-11.81061861527306</v>
       </c>
       <c r="E2">
-        <v>-11.34891494223246</v>
+        <v>-14.40546281539766</v>
       </c>
       <c r="F2">
-        <v>-2.550592254143951</v>
+        <v>-2.302265930867521</v>
       </c>
       <c r="G2">
-        <v>-8.870915909459642</v>
+        <v>-9.921497428362651</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.25385920593668</v>
       </c>
       <c r="E3">
-        <v>-11.65439674184189</v>
+        <v>-13.92342034270317</v>
       </c>
       <c r="F3">
-        <v>-2.631370501427944</v>
+        <v>-2.616569232674723</v>
       </c>
       <c r="G3">
-        <v>-9.374757323577057</v>
+        <v>-9.344717740200339</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.75956087171292</v>
       </c>
       <c r="E4">
-        <v>-12.54524720557882</v>
+        <v>-15.75580395127088</v>
       </c>
       <c r="F4">
-        <v>-2.414963659283587</v>
+        <v>-2.502685282137847</v>
       </c>
       <c r="G4">
-        <v>-9.006984886308254</v>
+        <v>-9.201850072280559</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.4052427234324</v>
       </c>
       <c r="E5">
-        <v>-13.02286535916781</v>
+        <v>-15.95033360921837</v>
       </c>
       <c r="F5">
-        <v>-2.705043841498127</v>
+        <v>-2.767001581390516</v>
       </c>
       <c r="G5">
-        <v>-8.834819191084192</v>
+        <v>-9.11497316905114</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.15939294475867</v>
       </c>
       <c r="E6">
-        <v>-14.61476888403218</v>
+        <v>-16.40792232227144</v>
       </c>
       <c r="F6">
-        <v>-2.211281368813634</v>
+        <v>-2.466877444417033</v>
       </c>
       <c r="G6">
-        <v>-8.707258421739217</v>
+        <v>-9.569697977645227</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.02602335112112</v>
       </c>
       <c r="E7">
-        <v>-14.72587046533637</v>
+        <v>-17.85170851929293</v>
       </c>
       <c r="F7">
-        <v>-2.185080107863086</v>
+        <v>-2.709120237487303</v>
       </c>
       <c r="G7">
-        <v>-8.213674106216628</v>
+        <v>-8.653646542679452</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.985096699405418</v>
       </c>
       <c r="E8">
-        <v>-14.84540406524284</v>
+        <v>-16.86943722228916</v>
       </c>
       <c r="F8">
-        <v>-2.289870241052029</v>
+        <v>-2.433765942592331</v>
       </c>
       <c r="G8">
-        <v>-8.819220263790591</v>
+        <v>-9.654543804729348</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.0179990999366</v>
       </c>
       <c r="E9">
-        <v>-15.41307545294836</v>
+        <v>-18.96302774009329</v>
       </c>
       <c r="F9">
-        <v>-2.082571298501453</v>
+        <v>-1.773938999933816</v>
       </c>
       <c r="G9">
-        <v>-8.328457798809122</v>
+        <v>-9.490640225391966</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.10827901508993</v>
       </c>
       <c r="E10">
-        <v>-16.25107862501578</v>
+        <v>-18.13923944793596</v>
       </c>
       <c r="F10">
-        <v>-1.801084599723555</v>
+        <v>-1.675564572279554</v>
       </c>
       <c r="G10">
-        <v>-8.236682031791455</v>
+        <v>-9.231312160662812</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.2236033615179</v>
       </c>
       <c r="E11">
-        <v>-15.43525139016392</v>
+        <v>-17.89742799287437</v>
       </c>
       <c r="F11">
-        <v>-1.88266802012307</v>
+        <v>-1.859829930827888</v>
       </c>
       <c r="G11">
-        <v>-8.084351320894234</v>
+        <v>-7.836448469635066</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.3555218899266</v>
       </c>
       <c r="E12">
-        <v>-17.06272154988454</v>
+        <v>-20.53247456235363</v>
       </c>
       <c r="F12">
-        <v>-1.251825652888509</v>
+        <v>-1.099599888745656</v>
       </c>
       <c r="G12">
-        <v>-8.383936692936214</v>
+        <v>-8.417070468243487</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.46970273662966</v>
       </c>
       <c r="E13">
-        <v>-17.50708711883521</v>
+        <v>-20.09864675241881</v>
       </c>
       <c r="F13">
-        <v>-1.425157390087292</v>
+        <v>-1.127631841656391</v>
       </c>
       <c r="G13">
-        <v>-7.472455999602745</v>
+        <v>-8.520123793760968</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.5623134746855</v>
       </c>
       <c r="E14">
-        <v>-18.0922701155284</v>
+        <v>-21.33454882164419</v>
       </c>
       <c r="F14">
-        <v>-1.316954383198815</v>
+        <v>-1.464779859697998</v>
       </c>
       <c r="G14">
-        <v>-7.42893387683827</v>
+        <v>-8.460254625187339</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.61130712269824</v>
       </c>
       <c r="E15">
-        <v>-18.99846757767732</v>
+        <v>-20.58604188139036</v>
       </c>
       <c r="F15">
-        <v>-1.298427946235204</v>
+        <v>-1.372614874095122</v>
       </c>
       <c r="G15">
-        <v>-7.303450120740426</v>
+        <v>-8.219583586245188</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.61486346000235</v>
       </c>
       <c r="E16">
-        <v>-19.22557960611001</v>
+        <v>-21.9317277459837</v>
       </c>
       <c r="F16">
-        <v>-0.9486647210163631</v>
+        <v>-1.045102425682879</v>
       </c>
       <c r="G16">
-        <v>-6.749579921506158</v>
+        <v>-8.6168377992256</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.57117969941107</v>
       </c>
       <c r="E17">
-        <v>-19.63883003015397</v>
+        <v>-21.69453080593593</v>
       </c>
       <c r="F17">
-        <v>-0.9831422006882814</v>
+        <v>-0.3554368608081224</v>
       </c>
       <c r="G17">
-        <v>-6.057169985589015</v>
+        <v>-7.02049726078327</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.48372076974259</v>
       </c>
       <c r="E18">
-        <v>-21.14927536456837</v>
+        <v>-22.01027412764674</v>
       </c>
       <c r="F18">
-        <v>-0.7484408644530974</v>
+        <v>-0.7172006445913197</v>
       </c>
       <c r="G18">
-        <v>-5.603062046648104</v>
+        <v>-6.710428385858863</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.37080069587524</v>
       </c>
       <c r="E19">
-        <v>-21.60358999091389</v>
+        <v>-23.43884465200246</v>
       </c>
       <c r="F19">
-        <v>-0.6590144614838769</v>
+        <v>-0.5769572149299607</v>
       </c>
       <c r="G19">
-        <v>-5.764534240809938</v>
+        <v>-7.021593188784125</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.23775443060956</v>
       </c>
       <c r="E20">
-        <v>-22.31929719393016</v>
+        <v>-23.81560010401861</v>
       </c>
       <c r="F20">
-        <v>-0.2605540017566614</v>
+        <v>-0.1290606169710735</v>
       </c>
       <c r="G20">
-        <v>-5.051209798672895</v>
+        <v>-6.954367521474222</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.11396215055275</v>
       </c>
       <c r="E21">
-        <v>-22.60444161677114</v>
+        <v>-27.0891071668913</v>
       </c>
       <c r="F21">
-        <v>0.06848181430933017</v>
+        <v>-0.07930969912633802</v>
       </c>
       <c r="G21">
-        <v>-5.254579910927278</v>
+        <v>-5.951258716093259</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.00126393068354</v>
       </c>
       <c r="E22">
-        <v>-24.15859578230758</v>
+        <v>-26.25564605425357</v>
       </c>
       <c r="F22">
-        <v>0.07962749771399752</v>
+        <v>0.3922674377763785</v>
       </c>
       <c r="G22">
-        <v>-5.164346318042549</v>
+        <v>-6.024656361156477</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.923075693478221</v>
       </c>
       <c r="E23">
-        <v>-24.80686947887563</v>
+        <v>-26.58276490267165</v>
       </c>
       <c r="F23">
-        <v>0.3076969245223686</v>
+        <v>0.782534515522504</v>
       </c>
       <c r="G23">
-        <v>-4.861410818788374</v>
+        <v>-5.099883439285698</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.874710160422918</v>
       </c>
       <c r="E24">
-        <v>-25.32120902819282</v>
+        <v>-27.05465000816693</v>
       </c>
       <c r="F24">
-        <v>0.6397140348710356</v>
+        <v>0.5266427127563059</v>
       </c>
       <c r="G24">
-        <v>-5.000767579639551</v>
+        <v>-6.292463102395236</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.86020407195088</v>
       </c>
       <c r="E25">
-        <v>-25.52808783475923</v>
+        <v>-27.55083490518738</v>
       </c>
       <c r="F25">
-        <v>0.7163330494255731</v>
+        <v>0.7727945716003874</v>
       </c>
       <c r="G25">
-        <v>-4.71282398169048</v>
+        <v>-6.172609922493399</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.868907198526871</v>
       </c>
       <c r="E26">
-        <v>-25.54883730266238</v>
+        <v>-27.75550834491205</v>
       </c>
       <c r="F26">
-        <v>0.4797819687799379</v>
+        <v>1.076449210444602</v>
       </c>
       <c r="G26">
-        <v>-4.824723480532223</v>
+        <v>-4.985480368394098</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.886569632134742</v>
       </c>
       <c r="E27">
-        <v>-25.3694916180626</v>
+        <v>-27.42638338250858</v>
       </c>
       <c r="F27">
-        <v>0.7431870638895275</v>
+        <v>0.7668833418140102</v>
       </c>
       <c r="G27">
-        <v>-5.768294520717062</v>
+        <v>-6.030710214933653</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.902032269382243</v>
       </c>
       <c r="E28">
-        <v>-25.18389663933224</v>
+        <v>-28.59088047358101</v>
       </c>
       <c r="F28">
-        <v>0.8116102113607666</v>
+        <v>1.246708532946401</v>
       </c>
       <c r="G28">
-        <v>-5.080648918504233</v>
+        <v>-5.239450198316678</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.891209129148521</v>
       </c>
       <c r="E29">
-        <v>-25.36786136741984</v>
+        <v>-27.54991109648981</v>
       </c>
       <c r="F29">
-        <v>0.6598417060242581</v>
+        <v>0.5893211322891305</v>
       </c>
       <c r="G29">
-        <v>-5.503805094474902</v>
+        <v>-6.024787610018855</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.84882403914369</v>
       </c>
       <c r="E30">
-        <v>-24.66420896221199</v>
+        <v>-27.66288746603317</v>
       </c>
       <c r="F30">
-        <v>0.7327877395147825</v>
+        <v>0.3042326920438611</v>
       </c>
       <c r="G30">
-        <v>-5.956833511522755</v>
+        <v>-5.261627974836966</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.750234771167744</v>
       </c>
       <c r="E31">
-        <v>-25.33578618602351</v>
+        <v>-26.93522056316264</v>
       </c>
       <c r="F31">
-        <v>0.4557717396097942</v>
+        <v>0.5374454520562143</v>
       </c>
       <c r="G31">
-        <v>-5.595863046546683</v>
+        <v>-5.918282439420839</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.597902221277947</v>
       </c>
       <c r="E32">
-        <v>-25.34290947563758</v>
+        <v>-26.53271620793888</v>
       </c>
       <c r="F32">
-        <v>0.4394371627939908</v>
+        <v>0.3311786552895262</v>
       </c>
       <c r="G32">
-        <v>-6.029466631962624</v>
+        <v>-7.223033942761555</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.379104813916044</v>
       </c>
       <c r="E33">
-        <v>-24.67909858474921</v>
+        <v>-27.35044993034796</v>
       </c>
       <c r="F33">
-        <v>0.2643302342510089</v>
+        <v>0.7969398246571874</v>
       </c>
       <c r="G33">
-        <v>-6.153181809639927</v>
+        <v>-6.139794425677392</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.102376856119418</v>
       </c>
       <c r="E34">
-        <v>-23.11676146668091</v>
+        <v>-26.32019945123292</v>
       </c>
       <c r="F34">
-        <v>0.3664190613394228</v>
+        <v>0.5233441537583583</v>
       </c>
       <c r="G34">
-        <v>-6.11771180458233</v>
+        <v>-6.486471889540524</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.772207192505174</v>
       </c>
       <c r="E35">
-        <v>-23.69247089575005</v>
+        <v>-26.76893046912698</v>
       </c>
       <c r="F35">
-        <v>0.3791775760773408</v>
+        <v>0.09629176475611517</v>
       </c>
       <c r="G35">
-        <v>-5.927660170637732</v>
+        <v>-6.766337120010242</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.401789797064675</v>
       </c>
       <c r="E36">
-        <v>-23.65232597367206</v>
+        <v>-26.32110967450846</v>
       </c>
       <c r="F36">
-        <v>0.27318382505213</v>
+        <v>0.2364109393070543</v>
       </c>
       <c r="G36">
-        <v>-5.907959716394826</v>
+        <v>-6.126646570888697</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.008887767128282</v>
       </c>
       <c r="E37">
-        <v>-23.48801029430374</v>
+        <v>-26.09009410148116</v>
       </c>
       <c r="F37">
-        <v>-0.0191785093571219</v>
+        <v>0.2107870504362573</v>
       </c>
       <c r="G37">
-        <v>-5.970316050910514</v>
+        <v>-5.252863832051688</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.60491488437044</v>
       </c>
       <c r="E38">
-        <v>-23.31068883758539</v>
+        <v>-25.0121904903834</v>
       </c>
       <c r="F38">
-        <v>0.1590521926618169</v>
+        <v>0.2600525449829522</v>
       </c>
       <c r="G38">
-        <v>-5.957210852002091</v>
+        <v>-6.653860126174036</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.215150923648141</v>
       </c>
       <c r="E39">
-        <v>-22.33853867998875</v>
+        <v>-24.21314578020398</v>
       </c>
       <c r="F39">
-        <v>0.4175748902993062</v>
+        <v>0.2272955844066486</v>
       </c>
       <c r="G39">
-        <v>-5.414237589566739</v>
+        <v>-5.435165220672878</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.845501393211804</v>
       </c>
       <c r="E40">
-        <v>-22.23171650662182</v>
+        <v>-24.913949775261</v>
       </c>
       <c r="F40">
-        <v>0.06078462440251717</v>
+        <v>0.5827554922545416</v>
       </c>
       <c r="G40">
-        <v>-5.643217636092588</v>
+        <v>-6.232055813485859</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.520297845068035</v>
       </c>
       <c r="E41">
-        <v>-22.35545705888141</v>
+        <v>-22.4104146194385</v>
       </c>
       <c r="F41">
-        <v>0.07816874271766759</v>
+        <v>0.8248707167447812</v>
       </c>
       <c r="G41">
-        <v>-4.697477708456957</v>
+        <v>-6.051424566638428</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.240925143842251</v>
       </c>
       <c r="E42">
-        <v>-22.17206291851878</v>
+        <v>-24.29728029879248</v>
       </c>
       <c r="F42">
-        <v>-0.2844093262224816</v>
+        <v>0.0694418921291748</v>
       </c>
       <c r="G42">
-        <v>-4.995196065431614</v>
+        <v>-5.87768388506583</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.020025275692256</v>
       </c>
       <c r="E43">
-        <v>-21.29198116597209</v>
+        <v>-23.36100924075862</v>
       </c>
       <c r="F43">
-        <v>-0.1096180056599663</v>
+        <v>0.3335809207576448</v>
       </c>
       <c r="G43">
-        <v>-4.48118942692304</v>
+        <v>-5.662904965449257</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.855376579197915</v>
       </c>
       <c r="E44">
-        <v>-21.5947413527029</v>
+        <v>-25.45034752146956</v>
       </c>
       <c r="F44">
-        <v>-0.13290921192448</v>
+        <v>0.3089659833834574</v>
       </c>
       <c r="G44">
-        <v>-4.38947928433656</v>
+        <v>-6.033719095103664</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.745501798703402</v>
       </c>
       <c r="E45">
-        <v>-20.40972574590172</v>
+        <v>-22.21188179046822</v>
       </c>
       <c r="F45">
-        <v>-0.004253813860883213</v>
+        <v>0.466518978293715</v>
       </c>
       <c r="G45">
-        <v>-5.098590637991276</v>
+        <v>-5.222732374471308</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.687341033807337</v>
       </c>
       <c r="E46">
-        <v>-20.63607246222711</v>
+        <v>-23.14448931302988</v>
       </c>
       <c r="F46">
-        <v>-0.2394107521676069</v>
+        <v>0.259111519613372</v>
       </c>
       <c r="G46">
-        <v>-4.266889565654146</v>
+        <v>-5.001269606538147</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.668517664004324</v>
       </c>
       <c r="E47">
-        <v>-20.09103438761192</v>
+        <v>-23.09404211258443</v>
       </c>
       <c r="F47">
-        <v>-0.4231070223102169</v>
+        <v>0.1630001917035594</v>
       </c>
       <c r="G47">
-        <v>-4.325616869125088</v>
+        <v>-6.380573744931005</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.688778756568234</v>
       </c>
       <c r="E48">
-        <v>-19.52486192480293</v>
+        <v>-21.37034640867482</v>
       </c>
       <c r="F48">
-        <v>-0.7395027801768908</v>
+        <v>-0.2818869474809571</v>
       </c>
       <c r="G48">
-        <v>-4.620306658600377</v>
+        <v>-5.808414016724393</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.73148721101267</v>
       </c>
       <c r="E49">
-        <v>-19.70800699909514</v>
+        <v>-21.26255061339624</v>
       </c>
       <c r="F49">
-        <v>-0.5541207823695838</v>
+        <v>-0.1714647443203802</v>
       </c>
       <c r="G49">
-        <v>-4.230746910176863</v>
+        <v>-5.340049170107694</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.798756054815271</v>
       </c>
       <c r="E50">
-        <v>-18.92622483183296</v>
+        <v>-21.40267518461558</v>
       </c>
       <c r="F50">
-        <v>-0.6659760611370039</v>
+        <v>0.1954291187883544</v>
       </c>
       <c r="G50">
-        <v>-4.026313682137219</v>
+        <v>-5.960324731262005</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.87703638826522</v>
       </c>
       <c r="E51">
-        <v>-18.79841770991447</v>
+        <v>-20.9668050329033</v>
       </c>
       <c r="F51">
-        <v>-0.4839067045734922</v>
+        <v>0.3093279799384808</v>
       </c>
       <c r="G51">
-        <v>-4.077389176931535</v>
+        <v>-6.019170158709086</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.964484804570428</v>
       </c>
       <c r="E52">
-        <v>-18.94067519239143</v>
+        <v>-21.47248161144382</v>
       </c>
       <c r="F52">
-        <v>-0.629596649908258</v>
+        <v>0.06754078893974994</v>
       </c>
       <c r="G52">
-        <v>-4.883093130853185</v>
+        <v>-5.515479680783406</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.051379218654989</v>
       </c>
       <c r="E53">
-        <v>-17.57222468896154</v>
+        <v>-20.61415917650399</v>
       </c>
       <c r="F53">
-        <v>-0.8262411309240271</v>
+        <v>0.5190664644903017</v>
       </c>
       <c r="G53">
-        <v>-4.416201552716678</v>
+        <v>-5.319288881301087</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.130795456909071</v>
       </c>
       <c r="E54">
-        <v>-17.71419687757601</v>
+        <v>-19.35393467338341</v>
       </c>
       <c r="F54">
-        <v>-1.027749785329035</v>
+        <v>-0.1765376662951244</v>
       </c>
       <c r="G54">
-        <v>-4.836998530386106</v>
+        <v>-5.694526097617626</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.199791678424396</v>
       </c>
       <c r="E55">
-        <v>-17.85395464240074</v>
+        <v>-19.70749981000628</v>
       </c>
       <c r="F55">
-        <v>-0.7375842812720071</v>
+        <v>-0.3184916746432644</v>
       </c>
       <c r="G55">
-        <v>-4.485592826255814</v>
+        <v>-5.579847404115033</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.250884953382241</v>
       </c>
       <c r="E56">
-        <v>-16.69387734195979</v>
+        <v>-18.87139406854808</v>
       </c>
       <c r="F56">
-        <v>-0.7954838492580814</v>
+        <v>0.09270659063679892</v>
       </c>
       <c r="G56">
-        <v>-4.579370138424744</v>
+        <v>-5.527252703738694</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.289404585259</v>
       </c>
       <c r="E57">
-        <v>-17.06926066635162</v>
+        <v>-17.67147072531365</v>
       </c>
       <c r="F57">
-        <v>-1.055946583352927</v>
+        <v>-0.2933291864158267</v>
       </c>
       <c r="G57">
-        <v>-4.664117528862083</v>
+        <v>-6.46658112444717</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.307723690032377</v>
       </c>
       <c r="E58">
-        <v>-16.39813628994087</v>
+        <v>-18.41376912770296</v>
       </c>
       <c r="F58">
-        <v>-0.9587732884327256</v>
+        <v>-0.4200478614916783</v>
       </c>
       <c r="G58">
-        <v>-4.571849578610498</v>
+        <v>-6.262000241437351</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.313663083199557</v>
       </c>
       <c r="E59">
-        <v>-15.84883692128446</v>
+        <v>-18.06466453797764</v>
       </c>
       <c r="F59">
-        <v>-1.048725704702724</v>
+        <v>-0.04656267895886796</v>
       </c>
       <c r="G59">
-        <v>-4.916761745274647</v>
+        <v>-6.398446558765301</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.301708310658223</v>
       </c>
       <c r="E60">
-        <v>-16.93465630494762</v>
+        <v>-19.36127532974985</v>
       </c>
       <c r="F60">
-        <v>-1.103896630463977</v>
+        <v>-0.04235043071563248</v>
       </c>
       <c r="G60">
-        <v>-5.194421994856419</v>
+        <v>-6.494839004517108</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.278231993362338</v>
       </c>
       <c r="E61">
-        <v>-16.08143293174043</v>
+        <v>-18.74586476905546</v>
       </c>
       <c r="F61">
-        <v>-0.9902703021893712</v>
+        <v>-0.1724993752064768</v>
       </c>
       <c r="G61">
-        <v>-5.528450349607891</v>
+        <v>-6.479217108672592</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.243104579546835</v>
       </c>
       <c r="E62">
-        <v>-16.34362251983653</v>
+        <v>-18.24007045019074</v>
       </c>
       <c r="F62">
-        <v>-1.184271462822807</v>
+        <v>-0.2639246287186526</v>
       </c>
       <c r="G62">
-        <v>-5.684518371861319</v>
+        <v>-6.59610734550625</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.199896166025115</v>
       </c>
       <c r="E63">
-        <v>-16.29975066365022</v>
+        <v>-17.66172092077513</v>
       </c>
       <c r="F63">
-        <v>-1.265867308733364</v>
+        <v>-0.4334500177015715</v>
       </c>
       <c r="G63">
-        <v>-5.988576048888824</v>
+        <v>-7.546208016594384</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.153565642065963</v>
       </c>
       <c r="E64">
-        <v>-15.41985457853784</v>
+        <v>-16.90540236285807</v>
       </c>
       <c r="F64">
-        <v>-1.279059887990349</v>
+        <v>0.2072333542782474</v>
       </c>
       <c r="G64">
-        <v>-5.979218005001287</v>
+        <v>-7.646429647906063</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.102899908994306</v>
       </c>
       <c r="E65">
-        <v>-16.17225147796426</v>
+        <v>-16.80911794850699</v>
       </c>
       <c r="F65">
-        <v>-1.284740831638748</v>
+        <v>-0.51902616898258</v>
       </c>
       <c r="G65">
-        <v>-6.090425166093987</v>
+        <v>-8.140929424243739</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.056561159242888</v>
       </c>
       <c r="E66">
-        <v>-15.92153251452959</v>
+        <v>-18.01157270871171</v>
       </c>
       <c r="F66">
-        <v>-1.61744880040135</v>
+        <v>-0.2675122879401773</v>
       </c>
       <c r="G66">
-        <v>-5.816351291676689</v>
+        <v>-8.050065836819595</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.009509049699959</v>
       </c>
       <c r="E67">
-        <v>-14.61562023714563</v>
+        <v>-16.95949951335371</v>
       </c>
       <c r="F67">
-        <v>-1.516868430353434</v>
+        <v>-0.7720617609439254</v>
       </c>
       <c r="G67">
-        <v>-6.163356877695765</v>
+        <v>-8.368934947966434</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.971699233709599</v>
       </c>
       <c r="E68">
-        <v>-15.32227049214656</v>
+        <v>-17.18878973778408</v>
       </c>
       <c r="F68">
-        <v>-1.394431586382653</v>
+        <v>-0.3363189695189127</v>
       </c>
       <c r="G68">
-        <v>-6.418271699427465</v>
+        <v>-6.871792299709236</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.937382985171373</v>
       </c>
       <c r="E69">
-        <v>-14.9093234758611</v>
+        <v>-17.62749471422516</v>
       </c>
       <c r="F69">
-        <v>-1.611245985289187</v>
+        <v>-0.4918325238834778</v>
       </c>
       <c r="G69">
-        <v>-6.72008173968675</v>
+        <v>-7.913927954318234</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.912883592483915</v>
       </c>
       <c r="E70">
-        <v>-14.75680899975677</v>
+        <v>-16.8147921264386</v>
       </c>
       <c r="F70">
-        <v>-1.738729243477823</v>
+        <v>-1.372057382833038</v>
       </c>
       <c r="G70">
-        <v>-6.205031672722273</v>
+        <v>-8.166437640646862</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.894612625258199</v>
       </c>
       <c r="E71">
-        <v>-15.70648886932735</v>
+        <v>-16.1932952966779</v>
       </c>
       <c r="F71">
-        <v>-1.81421505142533</v>
+        <v>-0.7141936709191575</v>
       </c>
       <c r="G71">
-        <v>-6.831945145091339</v>
+        <v>-7.851384590173659</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.882556133240813</v>
       </c>
       <c r="E72">
-        <v>-15.90648892387611</v>
+        <v>-15.73773986845428</v>
       </c>
       <c r="F72">
-        <v>-1.807502790360446</v>
+        <v>-0.7763336516401624</v>
       </c>
       <c r="G72">
-        <v>-6.453197021706195</v>
+        <v>-9.346637254812615</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.876887930520072</v>
       </c>
       <c r="E73">
-        <v>-15.89404920577704</v>
+        <v>-16.5459909662913</v>
       </c>
       <c r="F73">
-        <v>-1.705372544901892</v>
+        <v>-1.346315037423641</v>
       </c>
       <c r="G73">
-        <v>-6.407410856065703</v>
+        <v>-8.694028536411537</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.87297884718852</v>
       </c>
       <c r="E74">
-        <v>-15.66559222056408</v>
+        <v>-17.65387307531984</v>
       </c>
       <c r="F74">
-        <v>-1.966222126573845</v>
+        <v>-0.9258556245802788</v>
       </c>
       <c r="G74">
-        <v>-6.331503076509509</v>
+        <v>-7.643991700287396</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.876235657643832</v>
       </c>
       <c r="E75">
-        <v>-15.91005736139415</v>
+        <v>-17.44029212722207</v>
       </c>
       <c r="F75">
-        <v>-2.309850462807553</v>
+        <v>-0.9722110644409391</v>
       </c>
       <c r="G75">
-        <v>-6.614974369473058</v>
+        <v>-7.437832549707484</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.878784911738719</v>
       </c>
       <c r="E76">
-        <v>-15.92952074267912</v>
+        <v>-16.51827217689035</v>
       </c>
       <c r="F76">
-        <v>-2.338829239659688</v>
+        <v>-1.443053439457372</v>
       </c>
       <c r="G76">
-        <v>-5.850633494529768</v>
+        <v>-8.292971387643728</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.888745905016091</v>
       </c>
       <c r="E77">
-        <v>-16.41879518836386</v>
+        <v>-18.56403295222547</v>
       </c>
       <c r="F77">
-        <v>-2.165277156731761</v>
+        <v>-1.424300858192797</v>
       </c>
       <c r="G77">
-        <v>-5.882257907919696</v>
+        <v>-7.684426193564433</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.898812834961597</v>
       </c>
       <c r="E78">
-        <v>-16.89253243972827</v>
+        <v>-17.96415958585141</v>
       </c>
       <c r="F78">
-        <v>-2.315625840339871</v>
+        <v>-1.936057127600901</v>
       </c>
       <c r="G78">
-        <v>-5.9883594882659</v>
+        <v>-8.773522691132204</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.915462076727881</v>
       </c>
       <c r="E79">
-        <v>-17.5782837871838</v>
+        <v>-18.81404094524094</v>
       </c>
       <c r="F79">
-        <v>-2.366466889686691</v>
+        <v>-1.50141854992382</v>
       </c>
       <c r="G79">
-        <v>-5.885821314533253</v>
+        <v>-7.769321238971946</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.936509172056923</v>
       </c>
       <c r="E80">
-        <v>-17.74111865555162</v>
+        <v>-19.45029154331862</v>
       </c>
       <c r="F80">
-        <v>-2.321396247667772</v>
+        <v>-1.56478202929876</v>
       </c>
       <c r="G80">
-        <v>-4.720413447157476</v>
+        <v>-7.697971076161821</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.964322592824876</v>
       </c>
       <c r="E81">
-        <v>-18.5223664628809</v>
+        <v>-19.03893402140986</v>
       </c>
       <c r="F81">
-        <v>-2.55358348883546</v>
+        <v>-1.23500399603986</v>
       </c>
       <c r="G81">
-        <v>-5.118806244019015</v>
+        <v>-6.927806032950516</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.002881404254253</v>
       </c>
       <c r="E82">
-        <v>-19.8128321154247</v>
+        <v>-21.55343261280494</v>
       </c>
       <c r="F82">
-        <v>-2.553359829636704</v>
+        <v>-2.222203393019545</v>
       </c>
       <c r="G82">
-        <v>-5.004271924265038</v>
+        <v>-7.40340597310579</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.051480335780106</v>
       </c>
       <c r="E83">
-        <v>-18.86057554414376</v>
+        <v>-21.6941006009052</v>
       </c>
       <c r="F83">
-        <v>-2.561743736120438</v>
+        <v>-2.113359229761302</v>
       </c>
       <c r="G83">
-        <v>-4.656770873790486</v>
+        <v>-6.787546936170493</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.122270826642048</v>
       </c>
       <c r="E84">
-        <v>-20.86902169365568</v>
+        <v>-21.55159405235782</v>
       </c>
       <c r="F84">
-        <v>-2.50099955447315</v>
+        <v>-1.535297119963514</v>
       </c>
       <c r="G84">
-        <v>-4.997850573673205</v>
+        <v>-6.451113446015948</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.211548627665862</v>
       </c>
       <c r="E85">
-        <v>-21.70863247399582</v>
+        <v>-22.71938787250784</v>
       </c>
       <c r="F85">
-        <v>-2.518029959907305</v>
+        <v>-1.735851495120497</v>
       </c>
       <c r="G85">
-        <v>-5.184755516142294</v>
+        <v>-6.696880222039916</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.334632979542137</v>
       </c>
       <c r="E86">
-        <v>-22.479197611141</v>
+        <v>-23.78829793422636</v>
       </c>
       <c r="F86">
-        <v>-2.782087808530301</v>
+        <v>-1.905750477802078</v>
       </c>
       <c r="G86">
-        <v>-5.093537556789731</v>
+        <v>-6.586470397786161</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.486502265745482</v>
       </c>
       <c r="E87">
-        <v>-23.59274936962714</v>
+        <v>-25.54357068739146</v>
       </c>
       <c r="F87">
-        <v>-2.677315899424219</v>
+        <v>-1.96556357448862</v>
       </c>
       <c r="G87">
-        <v>-4.338226603578033</v>
+        <v>-5.346667393993094</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.676869838251574</v>
       </c>
       <c r="E88">
-        <v>-25.49522017041156</v>
+        <v>-25.98982463000333</v>
       </c>
       <c r="F88">
-        <v>-2.693529534599214</v>
+        <v>-2.049932794463749</v>
       </c>
       <c r="G88">
-        <v>-4.42907050367282</v>
+        <v>-5.157180130156721</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.903967843419735</v>
       </c>
       <c r="E89">
-        <v>-26.64728207185893</v>
+        <v>-27.72263615209037</v>
       </c>
       <c r="F89">
-        <v>-2.689336338806243</v>
+        <v>-1.510799810760524</v>
       </c>
       <c r="G89">
-        <v>-4.977585749322074</v>
+        <v>-6.157408023008491</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.168559368306457</v>
       </c>
       <c r="E90">
-        <v>-27.41326439330836</v>
+        <v>-30.39171646797428</v>
       </c>
       <c r="F90">
-        <v>-3.013054864513664</v>
+        <v>-2.630271257884429</v>
       </c>
       <c r="G90">
-        <v>-4.465718467270258</v>
+        <v>-5.962939864844881</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.473307237754252</v>
       </c>
       <c r="E91">
-        <v>-29.79751501529481</v>
+        <v>-31.39116200265214</v>
       </c>
       <c r="F91">
-        <v>-2.86669062811302</v>
+        <v>-2.496849433785124</v>
       </c>
       <c r="G91">
-        <v>-4.978724333203202</v>
+        <v>-6.339988315462233</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.810880154816318</v>
       </c>
       <c r="E92">
-        <v>-30.99779157950185</v>
+        <v>-32.15671864754485</v>
       </c>
       <c r="F92">
-        <v>-2.897571336521982</v>
+        <v>-1.916379259947399</v>
       </c>
       <c r="G92">
-        <v>-4.282268651103263</v>
+        <v>-5.629065727506704</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.19094759416557</v>
       </c>
       <c r="E93">
-        <v>-32.24446462415447</v>
+        <v>-32.8711171215729</v>
       </c>
       <c r="F93">
-        <v>-3.14111218131244</v>
+        <v>-2.457817590132615</v>
       </c>
       <c r="G93">
-        <v>-4.904588413289107</v>
+        <v>-5.192932320268431</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.60003625376968</v>
       </c>
       <c r="E94">
-        <v>-34.81941381507794</v>
+        <v>-36.47125169343383</v>
       </c>
       <c r="F94">
-        <v>-2.775300166031761</v>
+        <v>-2.626132734340043</v>
       </c>
       <c r="G94">
-        <v>-4.842140204569755</v>
+        <v>-6.041840118463289</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.04899375071955</v>
       </c>
       <c r="E95">
-        <v>-36.42997012437991</v>
+        <v>-36.49629189045925</v>
       </c>
       <c r="F95">
-        <v>-3.130743506531598</v>
+        <v>-2.17141701592131</v>
       </c>
       <c r="G95">
-        <v>-5.074148818594972</v>
+        <v>-6.666591265824682</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.527600550364298</v>
       </c>
       <c r="E96">
-        <v>-38.6332878316269</v>
+        <v>-39.7116307047034</v>
       </c>
       <c r="F96">
-        <v>-2.777839112121342</v>
+        <v>-2.687160217639089</v>
       </c>
       <c r="G96">
-        <v>-5.762706600401327</v>
+        <v>-6.781936047303843</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.03319551600362</v>
       </c>
       <c r="E97">
-        <v>-41.17532407346262</v>
+        <v>-42.49478780931454</v>
       </c>
       <c r="F97">
-        <v>-3.143700829446188</v>
+        <v>-2.255532755471183</v>
       </c>
       <c r="G97">
-        <v>-5.52319383266966</v>
+        <v>-6.879644262900987</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.56802846130806</v>
       </c>
       <c r="E98">
-        <v>-43.23562351459937</v>
+        <v>-44.55545632108291</v>
       </c>
       <c r="F98">
-        <v>-2.870781106348044</v>
+        <v>-2.426197149632952</v>
       </c>
       <c r="G98">
-        <v>-6.339824254384261</v>
+        <v>-6.545071225370648</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.10812012720634</v>
       </c>
       <c r="E99">
-        <v>-45.14169218798288</v>
+        <v>-43.68759012717191</v>
       </c>
       <c r="F99">
-        <v>-3.024040673009591</v>
+        <v>-2.685218524446926</v>
       </c>
       <c r="G99">
-        <v>-6.033702688995866</v>
+        <v>-6.955762040636985</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.68036939255014</v>
       </c>
       <c r="E100">
-        <v>-47.42386194888843</v>
+        <v>-46.1712837741298</v>
       </c>
       <c r="F100">
-        <v>-3.117767131166744</v>
+        <v>-2.55700133273941</v>
       </c>
       <c r="G100">
-        <v>-6.984610540587624</v>
+        <v>-7.206647522293688</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.22431796850778</v>
       </c>
       <c r="E101">
-        <v>-48.91832290217426</v>
+        <v>-49.99534572507753</v>
       </c>
       <c r="F101">
-        <v>-2.98626297760492</v>
+        <v>-2.433042777849687</v>
       </c>
       <c r="G101">
-        <v>-6.785069613893112</v>
+        <v>-7.952918710109116</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.82411746855809</v>
       </c>
       <c r="E102">
-        <v>-51.16668081190154</v>
+        <v>-52.28888988057184</v>
       </c>
       <c r="F102">
-        <v>-2.728692074113247</v>
+        <v>-3.112455639379994</v>
       </c>
       <c r="G102">
-        <v>-7.433209308530227</v>
+        <v>-8.002251876255366</v>
       </c>
     </row>
   </sheetData>
